--- a/college-posters/data/字段表_第四批.xlsx
+++ b/college-posters/data/字段表_第四批.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -854,17 +854,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>软科中国大学排名</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2026年名次未查到；海报暂用2025年第56名并标注年份（2024年第57名）</t>
+          <t>海洋科学、水产养殖学、海洋技术、船舶与海洋工程、大气科学、食品科学与工程</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>待核软科2026名次</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -876,17 +876,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>海洋科学、水产养殖学、海洋技术、船舶与海洋工程、大气科学、食品科学与工程</t>
+          <t>海洋与水产科研院所、海洋工程与船舶、党政机关与国企</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>知名校友</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>海洋与水产科研院所、海洋工程与船舶、党政机关与国企</t>
+          <t>管华诗（山东海洋学院水产系）；包振民（山东海洋学院）</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核（学籍）</t>
         </is>
       </c>
     </row>
@@ -920,17 +920,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>管华诗（山东海洋学院水产系）；包振民（山东海洋学院）</t>
+          <t>一多楼：闻一多曾在此居住；鱼山校区：临海的老校区；崂山校区：崂山脚下的主校区</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>待核（学籍）</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -942,39 +942,39 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>一多楼：闻一多曾在此居住；鱼山校区：临海的老校区；崂山校区：崂山脚下的主校区</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>中国海洋大学</t>
+          <t>西北农林科技大学</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>第4张排名卡</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>双一流学科海报写2个（植物保护、畜牧学）；办学92年</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核教育部名单原文（个数未核到）</t>
         </is>
       </c>
     </row>
@@ -986,17 +986,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>第4张排名卡</t>
+          <t>双一流建设学科</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>双一流学科海报写2个（植物保护、畜牧学）；办学92年</t>
+          <t>植物保护、畜牧学</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>待核教育部名单原文（个数未核到）</t>
+          <t>待核教育部名单原文</t>
         </is>
       </c>
     </row>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>双一流建设学科</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>植物保护、畜牧学</t>
+          <t>农学、植物保护、动物科学、葡萄与葡萄酒工程、园艺、水利水电工程</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>待核教育部名单原文</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -1030,17 +1030,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>农学、植物保护、动物科学、葡萄与葡萄酒工程、园艺、水利水电工程</t>
+          <t>农业科研院所、食品与农业企业、党政机关与国企</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -1052,17 +1052,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>知名校友</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>农业科研院所、食品与农业企业、党政机关与国企</t>
+          <t>康振生（西北农学院植保系）；吴普特（西北农业大学，原校长）</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核（学籍）</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>康振生（西北农学院植保系）；吴普特（西北农业大学，原校长）</t>
+          <t>三号教学楼：上世纪30年代老楼；博览园：昆虫、动植物博物馆群；杨凌示范区：国家农业高新技术示范区</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>待核（学籍）</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -1096,39 +1096,39 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>三号教学楼：上世纪30年代老楼；博览园：昆虫、动植物博物馆群；杨凌示范区：国家农业高新技术示范区</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>西北农林科技大学</t>
+          <t>中央民族大学</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>民族学、汉语言文学、中国少数民族语言文学、舞蹈学、经济学、法学</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -1140,17 +1140,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>民族学、汉语言文学、中国少数民族语言文学、舞蹈学、经济学、法学</t>
+          <t>党政机关与事业单位、教育与文化传媒、民族地区发展</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -1162,17 +1162,17 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>党政机关与事业单位、教育与文化传媒、民族地区发展</t>
+          <t>民族博物馆：展示各民族文化文物；海淀校区：魏公村主校区；丰台校区：新建校区</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -1184,37 +1184,15 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>民族博物馆：展示各民族文化文物；海淀校区：魏公村主校区；丰台校区：新建校区</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>中央民族大学</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>待核2027年招生章程</t>
         </is>
@@ -4479,22 +4457,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026年名次未查到；海报暂用2025年第56名并标注年份（2024年第57名）</t>
+          <t>2026年主榜第51名（2025年第56名，2024年第57名）；第四批初稿曾误用2025年名次，已更正</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56名（2025）</t>
+          <t>51名（2026）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>大学生必备网整理</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>待核软科2026名次</t>
+          <t>2026软科主榜前100名（多源转载一致）</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>已核（多源一致）</t>
         </is>
       </c>
     </row>

--- a/college-posters/data/字段表_第四批.xlsx
+++ b/college-posters/data/字段表_第四批.xlsx
@@ -5978,7 +5978,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>不放（未查到可靠名次）</t>
+          <t>1名（2026）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1名；1个；85年</t>
+          <t>1个；85年</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">

--- a/college-posters/data/字段表_第四批.xlsx
+++ b/college-posters/data/字段表_第四批.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -502,68 +502,68 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>电子信息与通信、集成电路与芯片、互联网与软件</t>
+          <t>清水河校区：高新西区主校区；沙河校区：成电老校区；银杏大道：清水河校区秋季景观</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>电子科技大学</t>
+          <t>重庆大学</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>清水河校区：高新西区主校区；沙河校区：成电老校区；银杏大道：清水河校区秋季景观</t>
+          <t>电气工程及其自动化、机械设计制造及其自动化、建筑学、土木工程、车辆工程、计算机科学与技术</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>电子科技大学</t>
+          <t>重庆大学</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>民主湖：A区校园湖景；A区：嘉陵江畔的老校区；虎溪校区：大学城主校区</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>重庆大学</t>
+          <t>兰州大学</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>电气工程及其自动化、机械设计制造及其自动化、建筑学、土木工程、车辆工程、计算机科学与技术</t>
+          <t>化学、大气科学、草业科学、生态学、临床医学、核化工与核燃料工程</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -585,51 +585,51 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>重庆大学</t>
+          <t>兰州大学</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>电力能源与制造、建筑与土木工程、汽车与电子信息</t>
+          <t>积石堂：1940年代图书馆旧址；榆中校区：兰大主校区；城关校区：兰州市区老校区</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>重庆大学</t>
+          <t>东北大学</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>鲜学福（重庆大学采矿系）；周绪红（重庆建筑工程学院）</t>
+          <t>冶金工程、自动化、计算机科学与技术、软件工程、材料成型及控制工程、采矿工程</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>待核（学籍）</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>重庆大学</t>
+          <t>东北大学</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>民主湖：A区校园湖景；A区：嘉陵江畔的老校区；虎溪校区：大学城主校区</t>
+          <t>汉卿会堂：纪念张学良校长；南湖校区：沈阳老校区；浑南校区：新建主校区</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -651,73 +651,73 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>重庆大学</t>
+          <t>中国海洋大学</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>海洋科学、水产养殖学、海洋技术、船舶与海洋工程、大气科学、食品科学与工程</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>兰州大学</t>
+          <t>中国海洋大学</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>化学、大气科学、草业科学、生态学、临床医学、核化工与核燃料工程</t>
+          <t>一多楼：闻一多曾在此居住；鱼山校区：临海的老校区；崂山校区：崂山脚下的主校区</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>兰州大学</t>
+          <t>西北农林科技大学</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>科研院所与高校、党政机关与国企、能源与核工业</t>
+          <t>农学、植物保护、动物科学、葡萄与葡萄酒工程、园艺、水利水电工程</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>兰州大学</t>
+          <t>西北农林科技大学</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>积石堂：1940年代图书馆旧址；榆中校区：兰大主校区；城关校区：兰州市区老校区</t>
+          <t>三号教学楼：上世纪30年代老楼；博览园：昆虫、动植物博物馆群；杨凌示范区：国家农业高新技术示范区</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -739,462 +739,44 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>兰州大学</t>
+          <t>中央民族大学</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>民族学、汉语言文学、中国少数民族语言文学、舞蹈学、经济学、法学</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>东北大学</t>
+          <t>中央民族大学</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>冶金工程、自动化、计算机科学与技术、软件工程、材料成型及控制工程、采矿工程</t>
+          <t>民族博物馆：展示各民族文化文物；海淀校区：魏公村主校区；丰台校区：新建校区</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>东北大学</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>钢铁冶金与材料、自动化与智能制造、电子信息与软件</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>东北大学</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>汉卿会堂：纪念张学良校长；南湖校区：沈阳老校区；浑南校区：新建主校区</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
           <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>东北大学</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>中国海洋大学</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>海洋科学、水产养殖学、海洋技术、船舶与海洋工程、大气科学、食品科学与工程</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>中国海洋大学</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>海洋与水产科研院所、海洋工程与船舶、党政机关与国企</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>中国海洋大学</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>知名校友</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>管华诗（山东海洋学院水产系）；包振民（山东海洋学院）</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>待核（学籍）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>中国海洋大学</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>一多楼：闻一多曾在此居住；鱼山校区：临海的老校区；崂山校区：崂山脚下的主校区</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>中国海洋大学</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>西北农林科技大学</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>第4张排名卡</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>双一流学科海报写2个（植物保护、畜牧学）；办学92年</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文（个数未核到）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>西北农林科技大学</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>双一流建设学科</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>植物保护、畜牧学</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>西北农林科技大学</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>农学、植物保护、动物科学、葡萄与葡萄酒工程、园艺、水利水电工程</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>西北农林科技大学</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>农业科研院所、食品与农业企业、党政机关与国企</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>西北农林科技大学</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>知名校友</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>康振生（西北农学院植保系）；吴普特（西北农业大学，原校长）</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>待核（学籍）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>西北农林科技大学</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>三号教学楼：上世纪30年代老楼；博览园：昆虫、动植物博物馆群；杨凌示范区：国家农业高新技术示范区</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>西北农林科技大学</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>中央民族大学</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>民族学、汉语言文学、中国少数民族语言文学、舞蹈学、经济学、法学</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>中央民族大学</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>党政机关与事业单位、教育与文化传媒、民族地区发展</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>中央民族大学</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>民族博物馆：展示各民族文化文物；海淀校区：魏公村主校区；丰台校区：新建校区</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>中央民族大学</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
@@ -1758,9 +1340,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -1883,12 +1465,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -2516,9 +2098,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -2530,27 +2112,27 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>特色亮点（替代知名校友）</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>鲜学福（重庆大学采矿系）；周绪红（重庆建筑工程学院）</t>
+          <t>鲜学福毕业于北京矿业学院（重大任教）、周绪红学籍未核到，均撤下；改放国家重点实验室、双一流学科、虎溪校区</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>鲜学福 中国工程院院士；周绪红 中国工程院院士</t>
+          <t>国家重点实验室 输配电装备及系统安全与新技术；电气工程 国家双一流建设学科；虎溪校区 大学城主校区</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>学校官网、权威媒体</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>待核（学籍）</t>
+          <t>学校官网、公开资料</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（已更正）</t>
         </is>
       </c>
     </row>
@@ -2641,12 +2223,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -3274,9 +2856,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -3399,12 +2981,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -4032,9 +3614,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -4157,12 +3739,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -4790,9 +4372,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -4809,12 +4391,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>管华诗（山东海洋学院水产系）；包振民（山东海洋学院）</t>
+          <t>管华诗（1964年山东海洋学院水产品加工专业）；包振民学籍未核到，已撤下</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>管华诗 中国工程院院士；包振民 中国工程院院士</t>
+          <t>管华诗 中国工程院院士</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -4822,9 +4404,9 @@
           <t>学校官网、权威媒体</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>待核（学籍）</t>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>已核（已更正）</t>
         </is>
       </c>
     </row>
@@ -4915,12 +4497,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -5311,7 +4893,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>双一流学科海报写2个（植物保护、畜牧学）；办学92年</t>
+          <t>双一流2个：植物保护、畜牧学</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -5324,9 +4906,9 @@
           <t>教育部 教研函〔2022〕1号 名单（转载）</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文（个数未核到）</t>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>已核</t>
         </is>
       </c>
     </row>
@@ -5388,9 +4970,9 @@
           <t>教育部 第二轮双一流名单（转载）</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>已核</t>
         </is>
       </c>
     </row>
@@ -5548,9 +5130,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -5567,12 +5149,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>康振生（西北农学院植保系）；吴普特（西北农业大学，原校长）</t>
+          <t>康振生（1981年西北农学院植保专业）；吴普特学籍未核到，已撤下</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>康振生 中国工程院院士；吴普特 西北农林科大原校长</t>
+          <t>康振生 中国工程院院士</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -5580,9 +5162,9 @@
           <t>学校官网、权威媒体</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>待核（学籍）</t>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>已核</t>
         </is>
       </c>
     </row>
@@ -5673,12 +5255,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -6306,9 +5888,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -6431,12 +6013,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
